--- a/4 External Data/Massachusetts 2050 Decarbonization Roadmap Study/Figure 62 - Report.xlsx
+++ b/4 External Data/Massachusetts 2050 Decarbonization Roadmap Study/Figure 62 - Report.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amirgazar/Documents/GitHub/Decarbonization-Tradeoffs/4 External Data/Massachusetts 2050 Decarbonization Roadmap Study/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E88C0F-82AE-6246-9D02-E8D34A385768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF904881-FCFE-FD47-8D18-2CF8BC873078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" activeTab="2" xr2:uid="{57CF73A6-EFC2-734A-A588-22BF54CAE4D9}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17440" xr2:uid="{57CF73A6-EFC2-734A-A588-22BF54CAE4D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Original table" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t xml:space="preserve">Table 23 Gross Massachusetts energy system cost (2018$B) by category in 2050 for each pathway </t>
   </si>
@@ -137,13 +136,20 @@
   </si>
   <si>
     <t>Billion 2018 USD</t>
+  </si>
+  <si>
+    <t>NPV (2024 USD 2%)</t>
+  </si>
+  <si>
+    <t>ALL OPTIONS (adjusted)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
@@ -205,12 +211,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -226,7 +238,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -239,6 +251,12 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -623,350 +641,392 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C071F895-7F02-3243-A51E-80E7E2AEFE37}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="10" max="10" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="4" max="4" width="22.5" customWidth="1"/>
+    <col min="10" max="10" width="21.5" customWidth="1"/>
+    <col min="11" max="11" width="21.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="14">
         <v>4.21</v>
       </c>
-      <c r="D2" s="5">
-        <v>4.21</v>
+      <c r="D2" s="14">
+        <v>0</v>
       </c>
       <c r="E2" s="5">
         <v>4.21</v>
       </c>
       <c r="F2" s="5">
+        <v>4.21</v>
+      </c>
+      <c r="G2" s="5">
         <v>1.68</v>
-      </c>
-      <c r="G2" s="5">
-        <v>4.21</v>
       </c>
       <c r="H2" s="5">
         <v>4.21</v>
       </c>
       <c r="I2" s="5">
+        <v>4.21</v>
+      </c>
+      <c r="J2" s="5">
         <v>4.1500000000000004</v>
       </c>
-      <c r="J2" s="5">
+      <c r="K2" s="5">
         <v>4.21</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="5">
         <v>0.16</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="14">
         <v>0.25</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="14">
+        <f t="shared" ref="D3:D18" si="0">C3*1.23375</f>
+        <v>0.30843749999999998</v>
+      </c>
+      <c r="E3" s="5">
         <v>0.37</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <v>0.21</v>
       </c>
-      <c r="F3" s="5">
+      <c r="G3" s="5">
         <v>0.33</v>
       </c>
-      <c r="G3" s="5">
+      <c r="H3" s="5">
         <v>2.31</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0.3</v>
       </c>
       <c r="I3" s="5">
         <v>0.3</v>
       </c>
       <c r="J3" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="K3" s="5">
         <v>0.17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="5">
         <v>3.29</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="14">
         <v>5.0599999999999996</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="14">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
         <v>5.0599999999999996</v>
       </c>
-      <c r="E4" s="5">
+      <c r="F4" s="5">
         <v>4.7</v>
       </c>
-      <c r="F4" s="5">
+      <c r="G4" s="5">
         <v>5.96</v>
-      </c>
-      <c r="G4" s="5">
-        <v>5.0599999999999996</v>
       </c>
       <c r="H4" s="5">
         <v>5.0599999999999996</v>
       </c>
       <c r="I4" s="5">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="J4" s="5">
         <v>4.4800000000000004</v>
       </c>
-      <c r="J4" s="5">
+      <c r="K4" s="5">
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="5">
         <v>1.71</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="14">
         <v>3.42</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="14">
+        <f t="shared" si="0"/>
+        <v>4.2194249999999993</v>
+      </c>
+      <c r="E5" s="5">
         <v>3.42</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="5">
         <v>2.91</v>
       </c>
-      <c r="F5" s="5">
+      <c r="G5" s="5">
         <v>3.96</v>
       </c>
-      <c r="G5" s="5">
+      <c r="H5" s="5">
         <v>4.17</v>
       </c>
-      <c r="H5" s="5">
+      <c r="I5" s="5">
         <v>3.38</v>
       </c>
-      <c r="I5" s="5">
+      <c r="J5" s="5">
         <v>3.22</v>
       </c>
-      <c r="J5" s="5">
+      <c r="K5" s="5">
         <v>3.48</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5">
         <v>2.64</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="14">
         <v>1.53</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="14">
+        <f t="shared" si="0"/>
+        <v>1.8876374999999999</v>
+      </c>
+      <c r="E6" s="5">
         <v>1.52</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="5">
         <v>1.53</v>
       </c>
-      <c r="F6" s="5">
+      <c r="G6" s="5">
         <v>1.58</v>
       </c>
-      <c r="G6" s="5">
+      <c r="H6" s="5">
         <v>1.53</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <v>1.52</v>
       </c>
-      <c r="I6" s="5">
+      <c r="J6" s="5">
         <v>1.89</v>
       </c>
-      <c r="J6" s="5">
+      <c r="K6" s="5">
         <v>1.52</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="5">
         <v>0.18</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="14">
         <v>0.17</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="14">
+        <f t="shared" si="0"/>
+        <v>0.20973749999999999</v>
+      </c>
+      <c r="E7" s="5">
         <v>0.16</v>
       </c>
-      <c r="E7" s="5">
+      <c r="F7" s="5">
         <v>0.17</v>
       </c>
-      <c r="F7" s="5">
+      <c r="G7" s="5">
         <v>0.19</v>
       </c>
-      <c r="G7" s="5">
+      <c r="H7" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H7" s="5">
+      <c r="I7" s="5">
         <v>0.16</v>
       </c>
-      <c r="I7" s="5">
+      <c r="J7" s="5">
         <v>0.13</v>
       </c>
-      <c r="J7" s="5">
+      <c r="K7" s="5">
         <v>0.17</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="5">
         <v>0.24</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="14">
         <v>0.54</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="14">
+        <f t="shared" si="0"/>
+        <v>0.66622499999999996</v>
+      </c>
+      <c r="E8" s="5">
         <v>1.29</v>
       </c>
-      <c r="E8" s="5">
+      <c r="F8" s="5">
         <v>0.53</v>
       </c>
-      <c r="F8" s="5">
+      <c r="G8" s="5">
         <v>0.5</v>
       </c>
-      <c r="G8" s="5">
+      <c r="H8" s="5">
         <v>0.53</v>
       </c>
-      <c r="H8" s="5">
+      <c r="I8" s="5">
         <v>0.45</v>
       </c>
-      <c r="I8" s="5">
+      <c r="J8" s="5">
         <v>0.6</v>
       </c>
-      <c r="J8" s="5">
+      <c r="K8" s="5">
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="5">
         <v>0.31</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="14">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="14">
+        <f t="shared" si="0"/>
+        <v>8.6362499999999995E-2</v>
+      </c>
+      <c r="E9" s="5">
         <v>0.06</v>
       </c>
-      <c r="E9" s="5">
+      <c r="F9" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F9" s="5">
+      <c r="G9" s="5">
         <v>0.06</v>
       </c>
-      <c r="G9" s="5">
+      <c r="H9" s="5">
         <v>0.1</v>
       </c>
-      <c r="H9" s="5">
+      <c r="I9" s="5">
         <v>0.06</v>
       </c>
-      <c r="I9" s="5">
+      <c r="J9" s="5">
         <v>0.05</v>
       </c>
-      <c r="J9" s="5">
+      <c r="K9" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="5">
         <v>0.05</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="14">
         <v>1.18</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="14">
+        <f t="shared" si="0"/>
+        <v>1.4558249999999997</v>
+      </c>
+      <c r="E10" s="5">
         <v>1.21</v>
       </c>
-      <c r="E10" s="5">
+      <c r="F10" s="5">
         <v>0.66</v>
       </c>
-      <c r="F10" s="5">
+      <c r="G10" s="5">
         <v>1.31</v>
       </c>
-      <c r="G10" s="5">
+      <c r="H10" s="5">
         <v>2.79</v>
       </c>
-      <c r="H10" s="5">
+      <c r="I10" s="5">
         <v>1.24</v>
       </c>
-      <c r="I10" s="5">
+      <c r="J10" s="5">
         <v>1.1200000000000001</v>
       </c>
-      <c r="J10" s="5">
+      <c r="K10" s="5">
         <v>0.95</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="5">
         <v>0.79</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="14">
         <v>0.79</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
         <v>0.79</v>
       </c>
-      <c r="E11" s="5">
+      <c r="F11" s="5">
         <v>1.9</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0.79</v>
       </c>
       <c r="G11" s="5">
         <v>0.79</v>
@@ -980,232 +1040,263 @@
       <c r="J11" s="5">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K11" s="5">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="5">
         <v>1.03</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="14">
         <v>2.46</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="14">
+        <f t="shared" si="0"/>
+        <v>3.0350249999999996</v>
+      </c>
+      <c r="E12" s="5">
         <v>2.41</v>
       </c>
-      <c r="E12" s="5">
+      <c r="F12" s="5">
         <v>2.5299999999999998</v>
       </c>
-      <c r="F12" s="5">
+      <c r="G12" s="5">
         <v>3.21</v>
       </c>
-      <c r="G12" s="5">
+      <c r="H12" s="5">
         <v>2.1</v>
       </c>
-      <c r="H12" s="5">
+      <c r="I12" s="5">
         <v>1.95</v>
       </c>
-      <c r="I12" s="5">
+      <c r="J12" s="5">
         <v>2.25</v>
       </c>
-      <c r="J12" s="5">
+      <c r="K12" s="5">
         <v>2.41</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="5">
         <v>0.28999999999999998</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="14">
         <v>0.74</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="14">
+        <f t="shared" si="0"/>
+        <v>0.91297499999999987</v>
+      </c>
+      <c r="E13" s="5">
         <v>0.75</v>
       </c>
-      <c r="E13" s="5">
+      <c r="F13" s="5">
         <v>0.7</v>
       </c>
-      <c r="F13" s="5">
+      <c r="G13" s="5">
         <v>0.83</v>
       </c>
-      <c r="G13" s="5">
+      <c r="H13" s="5">
         <v>0.59</v>
       </c>
-      <c r="H13" s="5">
+      <c r="I13" s="5">
         <v>1.03</v>
       </c>
-      <c r="I13" s="5">
+      <c r="J13" s="5">
         <v>0.57999999999999996</v>
       </c>
-      <c r="J13" s="5">
+      <c r="K13" s="5">
         <v>0.96</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
       <c r="B14" s="5">
         <v>0.01</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="14">
         <v>1.24</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="14">
+        <f t="shared" si="0"/>
+        <v>1.5298499999999999</v>
+      </c>
+      <c r="E14" s="5">
         <v>3.74</v>
       </c>
-      <c r="E14" s="5">
+      <c r="F14" s="5">
         <v>1.24</v>
       </c>
-      <c r="F14" s="5">
+      <c r="G14" s="5">
         <v>2.5299999999999998</v>
       </c>
-      <c r="G14" s="5">
+      <c r="H14" s="5">
         <v>0.85</v>
       </c>
-      <c r="H14" s="5">
+      <c r="I14" s="5">
         <v>1.33</v>
       </c>
-      <c r="I14" s="5">
+      <c r="J14" s="5">
         <v>3.69</v>
       </c>
-      <c r="J14" s="5">
+      <c r="K14" s="5">
         <v>0.98</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="5">
         <v>0.01</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="14">
         <v>0.11</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="14">
+        <f t="shared" si="0"/>
+        <v>0.13571249999999999</v>
+      </c>
+      <c r="E15" s="5">
         <v>1.46</v>
       </c>
-      <c r="E15" s="5">
+      <c r="F15" s="5">
         <v>0.11</v>
       </c>
-      <c r="F15" s="5">
+      <c r="G15" s="5">
         <v>0.17</v>
       </c>
-      <c r="G15" s="5">
+      <c r="H15" s="5">
         <v>0.1</v>
       </c>
-      <c r="H15" s="5">
+      <c r="I15" s="5">
         <v>0.32</v>
       </c>
-      <c r="I15" s="5">
+      <c r="J15" s="5">
         <v>1.03</v>
       </c>
-      <c r="J15" s="5">
+      <c r="K15" s="5">
         <v>0.13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="5">
         <v>1.8</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="14">
         <v>0.19</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="14">
+        <f t="shared" si="0"/>
+        <v>0.2344125</v>
+      </c>
+      <c r="E16" s="5">
         <v>0</v>
       </c>
-      <c r="E16" s="5">
+      <c r="F16" s="5">
         <v>0.19</v>
       </c>
-      <c r="F16" s="5">
+      <c r="G16" s="5">
         <v>0.23</v>
       </c>
-      <c r="G16" s="5">
+      <c r="H16" s="5">
         <v>0.15</v>
       </c>
-      <c r="H16" s="5">
+      <c r="I16" s="5">
         <v>0.18</v>
       </c>
-      <c r="I16" s="5">
+      <c r="J16" s="5">
         <v>0.48</v>
       </c>
-      <c r="J16" s="5">
+      <c r="K16" s="5">
         <v>0.18</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="5">
         <v>9.1300000000000008</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="14">
         <v>1.0900000000000001</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="14">
+        <f t="shared" si="0"/>
+        <v>1.3447875</v>
+      </c>
+      <c r="E17" s="5">
         <v>0</v>
       </c>
-      <c r="E17" s="5">
+      <c r="F17" s="5">
         <v>1.08</v>
       </c>
-      <c r="F17" s="5">
+      <c r="G17" s="5">
         <v>0.94</v>
       </c>
-      <c r="G17" s="5">
+      <c r="H17" s="5">
         <v>1.25</v>
       </c>
-      <c r="H17" s="5">
+      <c r="I17" s="5">
         <v>1.1000000000000001</v>
       </c>
-      <c r="I17" s="5">
+      <c r="J17" s="5">
         <v>0.05</v>
       </c>
-      <c r="J17" s="5">
+      <c r="K17" s="5">
         <v>1.52</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="5">
         <v>0.71</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="14">
         <v>0.85</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="14">
+        <f>C18*1.23375</f>
+        <v>1.0486875</v>
+      </c>
+      <c r="E18" s="5">
         <v>0.73</v>
       </c>
-      <c r="E18" s="5">
+      <c r="F18" s="5">
         <v>0.86</v>
       </c>
-      <c r="F18" s="5">
+      <c r="G18" s="5">
         <v>0.85</v>
       </c>
-      <c r="G18" s="5">
+      <c r="H18" s="5">
         <v>0.96</v>
       </c>
-      <c r="H18" s="5">
+      <c r="I18" s="5">
         <v>0.92</v>
       </c>
-      <c r="I18" s="5">
+      <c r="J18" s="5">
         <v>0.8</v>
       </c>
-      <c r="J18" s="5">
+      <c r="K18" s="5">
         <v>0.82</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
@@ -1213,60 +1304,77 @@
         <f>SUM(B2:B18)</f>
         <v>22.35</v>
       </c>
-      <c r="C19" s="6">
-        <f t="shared" ref="C19:J19" si="0">SUM(C2:C18)</f>
+      <c r="C19" s="15">
+        <f t="shared" ref="C19:K19" si="1">SUM(C2:C18)</f>
         <v>23.9</v>
       </c>
-      <c r="D19" s="6">
-        <f t="shared" si="0"/>
+      <c r="D19" s="15">
+        <f>SUM(D2:D18)</f>
+        <v>17.075099999999996</v>
+      </c>
+      <c r="E19" s="6">
+        <f t="shared" si="1"/>
         <v>27.180000000000003</v>
       </c>
-      <c r="E19" s="6">
-        <f t="shared" si="0"/>
+      <c r="F19" s="6">
+        <f t="shared" si="1"/>
         <v>23.6</v>
       </c>
-      <c r="F19" s="6">
-        <f t="shared" si="0"/>
+      <c r="G19" s="6">
+        <f t="shared" si="1"/>
         <v>25.120000000000005</v>
       </c>
-      <c r="G19" s="6">
-        <f t="shared" si="0"/>
+      <c r="H19" s="6">
+        <f t="shared" si="1"/>
         <v>27.560000000000002</v>
       </c>
-      <c r="H19" s="6">
-        <f t="shared" si="0"/>
+      <c r="I19" s="6">
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="I19" s="6">
-        <f t="shared" si="0"/>
+      <c r="J19" s="6">
+        <f t="shared" si="1"/>
         <v>25.610000000000003</v>
       </c>
-      <c r="J19" s="6">
-        <f t="shared" si="0"/>
+      <c r="K19" s="6">
+        <f t="shared" si="1"/>
         <v>23.709999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B20" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="16">
+        <f>PV(0.02,26,-C19)</f>
+        <v>480.89275462618264</v>
+      </c>
+      <c r="D20" s="16">
+        <f>PV(0.02,26,-D19)</f>
+        <v>343.56869767855767</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
@@ -1283,12 +1391,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7D5C1DE-E0BF-4C45-AB78-2854BC635638}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" bestFit="1" customWidth="1"/>
@@ -1464,6 +1573,15 @@
         <v>12.855674999999996</v>
       </c>
       <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="12">
+        <f>PV(0.03,26,-C13)</f>
+        <v>229.81887616123342</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
